--- a/Statistik_Jassen.xlsx
+++ b/Statistik_Jassen.xlsx
@@ -429,13 +429,13 @@
         <v>1</v>
       </c>
       <c r="G8" t="str">
-        <v>Chäli</v>
+        <v>Küng</v>
       </c>
       <c r="H8">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I8">
-        <v>0.2619047619047619</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -443,13 +443,13 @@
         <v>2</v>
       </c>
       <c r="G9" t="str">
-        <v>Küng</v>
+        <v>Chäli</v>
       </c>
       <c r="H9">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I9">
-        <v>0.3333333333333333</v>
+        <v>0.2777777777777778</v>
       </c>
     </row>
     <row r="10">
@@ -463,7 +463,7 @@
         <v>3</v>
       </c>
       <c r="I10">
-        <v>0.29545454545454547</v>
+        <v>0.2765957446808511</v>
       </c>
     </row>
     <row r="11">
@@ -477,7 +477,7 @@
         <v>1</v>
       </c>
       <c r="I11">
-        <v>0.2903225806451613</v>
+        <v>0.3163265306122449</v>
       </c>
     </row>
     <row r="14">
@@ -528,10 +528,10 @@
         <v>1</v>
       </c>
       <c r="B17" t="str">
-        <v>Chäli</v>
+        <v>Küng</v>
       </c>
       <c r="C17">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -543,7 +543,7 @@
         <v>Goonse</v>
       </c>
       <c r="H17">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I17">
         <v>1</v>
@@ -552,10 +552,10 @@
         <v>1</v>
       </c>
       <c r="L17" t="str">
-        <v>Chäli</v>
+        <v>Küng</v>
       </c>
       <c r="M17">
-        <v>6.75</v>
+        <v>6.692308</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -566,10 +566,10 @@
         <v>2</v>
       </c>
       <c r="B18" t="str">
-        <v>Küng</v>
+        <v>Chäli</v>
       </c>
       <c r="C18">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F18">
         <v>2</v>
@@ -578,16 +578,16 @@
         <v>Küng</v>
       </c>
       <c r="H18">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K18">
         <v>2</v>
       </c>
       <c r="L18" t="str">
-        <v>Küng</v>
+        <v>Chäli</v>
       </c>
       <c r="M18">
-        <v>6.666667</v>
+        <v>6.230769</v>
       </c>
     </row>
     <row r="19">
@@ -598,7 +598,7 @@
         <v>Goonse</v>
       </c>
       <c r="C19">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F19">
         <v>3</v>
@@ -616,7 +616,7 @@
         <v>Goonse</v>
       </c>
       <c r="M19">
-        <v>5.25</v>
+        <v>5.384615</v>
       </c>
     </row>
     <row r="20">
@@ -645,7 +645,7 @@
         <v>Fuchs</v>
       </c>
       <c r="M20">
-        <v>4.166667</v>
+        <v>3.846154</v>
       </c>
     </row>
     <row r="22">
@@ -691,10 +691,10 @@
         <v>1</v>
       </c>
       <c r="B23" t="str">
-        <v>Chäli</v>
+        <v>Küng</v>
       </c>
       <c r="C23">
-        <v>2.382353</v>
+        <v>2.416667</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -726,10 +726,10 @@
         <v>2</v>
       </c>
       <c r="B24" t="str">
-        <v>Küng</v>
+        <v>Chäli</v>
       </c>
       <c r="C24">
-        <v>2.352941</v>
+        <v>2.25</v>
       </c>
       <c r="F24">
         <v>2</v>
@@ -758,7 +758,7 @@
         <v>Goonse</v>
       </c>
       <c r="C25">
-        <v>1.852941</v>
+        <v>1.944444</v>
       </c>
       <c r="F25">
         <v>2</v>
@@ -787,7 +787,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C26">
-        <v>1.470588</v>
+        <v>1.388889</v>
       </c>
       <c r="F26">
         <v>4</v>
@@ -856,10 +856,10 @@
         <v>1</v>
       </c>
       <c r="B31" t="str">
-        <v>Chäli</v>
+        <v>Küng</v>
       </c>
       <c r="C31">
-        <v>102210</v>
+        <v>108906</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -868,10 +868,10 @@
         <v>1</v>
       </c>
       <c r="G31" t="str">
-        <v>Chäli</v>
+        <v>Küng</v>
       </c>
       <c r="H31">
-        <v>8517.5</v>
+        <v>8377.384615</v>
       </c>
       <c r="I31">
         <v>1</v>
@@ -880,10 +880,10 @@
         <v>1</v>
       </c>
       <c r="L31" t="str">
-        <v>Chäli</v>
+        <v>Küng</v>
       </c>
       <c r="M31">
-        <v>3006.176471</v>
+        <v>3025.166667</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -894,28 +894,28 @@
         <v>2</v>
       </c>
       <c r="B32" t="str">
-        <v>Küng</v>
+        <v>Chäli</v>
       </c>
       <c r="C32">
-        <v>102021</v>
+        <v>107710</v>
       </c>
       <c r="F32">
         <v>2</v>
       </c>
       <c r="G32" t="str">
-        <v>Küng</v>
+        <v>Chäli</v>
       </c>
       <c r="H32">
-        <v>8501.75</v>
+        <v>8285.384615</v>
       </c>
       <c r="K32">
         <v>2</v>
       </c>
       <c r="L32" t="str">
-        <v>Küng</v>
+        <v>Chäli</v>
       </c>
       <c r="M32">
-        <v>3000.617647</v>
+        <v>2991.944444</v>
       </c>
     </row>
     <row r="33">
@@ -926,7 +926,7 @@
         <v>Goonse</v>
       </c>
       <c r="C33">
-        <v>96754</v>
+        <v>103639</v>
       </c>
       <c r="F33">
         <v>3</v>
@@ -935,7 +935,7 @@
         <v>Goonse</v>
       </c>
       <c r="H33">
-        <v>8062.833333</v>
+        <v>7972.230769</v>
       </c>
       <c r="K33">
         <v>3</v>
@@ -944,7 +944,7 @@
         <v>Goonse</v>
       </c>
       <c r="M33">
-        <v>2845.705882</v>
+        <v>2878.861111</v>
       </c>
     </row>
     <row r="34">
@@ -955,7 +955,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C34">
-        <v>95639</v>
+        <v>101139</v>
       </c>
       <c r="F34">
         <v>4</v>
@@ -964,7 +964,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H34">
-        <v>7969.916667</v>
+        <v>7779.923077</v>
       </c>
       <c r="K34">
         <v>4</v>
@@ -973,7 +973,7 @@
         <v>Fuchs</v>
       </c>
       <c r="M34">
-        <v>2812.911765</v>
+        <v>2809.416667</v>
       </c>
     </row>
     <row r="36">
@@ -1027,7 +1027,7 @@
         <v>Küng</v>
       </c>
       <c r="C39">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1039,7 +1039,7 @@
         <v>Küng</v>
       </c>
       <c r="H39">
-        <v>15934</v>
+        <v>16448</v>
       </c>
       <c r="I39">
         <v>1</v>
@@ -1097,7 +1097,7 @@
         <v>Goonse</v>
       </c>
       <c r="C41">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F41">
         <v>3</v>
@@ -1106,7 +1106,7 @@
         <v>Goonse</v>
       </c>
       <c r="H41">
-        <v>11822</v>
+        <v>12336</v>
       </c>
       <c r="K41">
         <v>3</v>
@@ -1193,7 +1193,7 @@
         <v>Küng</v>
       </c>
       <c r="C45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -1228,7 +1228,7 @@
         <v>2</v>
       </c>
       <c r="B46" t="str">
-        <v>Chäli</v>
+        <v>Goonse</v>
       </c>
       <c r="C46">
         <v>5</v>
@@ -1254,13 +1254,13 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B47" t="str">
-        <v>Goonse</v>
+        <v>Chäli</v>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F47">
         <v>3</v>
@@ -1361,7 +1361,7 @@
         <v>Chäli</v>
       </c>
       <c r="C53">
-        <v>10310</v>
+        <v>10870</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -1373,7 +1373,7 @@
         <v>Chäli</v>
       </c>
       <c r="H53">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I53">
         <v>1</v>
@@ -1385,7 +1385,7 @@
         <v>Chäli</v>
       </c>
       <c r="M53">
-        <v>4060</v>
+        <v>4220</v>
       </c>
       <c r="N53">
         <v>1</v>
@@ -1399,7 +1399,7 @@
         <v>Küng</v>
       </c>
       <c r="C54">
-        <v>8200</v>
+        <v>9440</v>
       </c>
       <c r="F54">
         <v>2</v>
@@ -1408,7 +1408,7 @@
         <v>Küng</v>
       </c>
       <c r="H54">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K54">
         <v>2</v>
@@ -1417,7 +1417,7 @@
         <v>Küng</v>
       </c>
       <c r="M54">
-        <v>3700</v>
+        <v>4040</v>
       </c>
     </row>
     <row r="55">
@@ -1428,7 +1428,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C55">
-        <v>7810</v>
+        <v>8050</v>
       </c>
       <c r="F55">
         <v>3</v>
@@ -1437,7 +1437,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H55">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="K55">
         <v>3</v>
@@ -1446,7 +1446,7 @@
         <v>Fuchs</v>
       </c>
       <c r="M55">
-        <v>3660</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="56">
@@ -1457,7 +1457,7 @@
         <v>Goonse</v>
       </c>
       <c r="C56">
-        <v>5990</v>
+        <v>6340</v>
       </c>
       <c r="F56">
         <v>4</v>
@@ -1466,7 +1466,7 @@
         <v>Goonse</v>
       </c>
       <c r="H56">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K56">
         <v>4</v>
@@ -1475,7 +1475,7 @@
         <v>Goonse</v>
       </c>
       <c r="M56">
-        <v>3040</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="58">
@@ -1548,7 +1548,7 @@
         <v>Chäli</v>
       </c>
       <c r="M59">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N59">
         <v>1</v>
@@ -1591,7 +1591,7 @@
         <v>Küng</v>
       </c>
       <c r="C61">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F61">
         <v>3</v>
@@ -1600,7 +1600,7 @@
         <v>Küng</v>
       </c>
       <c r="H61">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="K61">
         <v>3</v>
@@ -1609,7 +1609,7 @@
         <v>Küng</v>
       </c>
       <c r="M61">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
@@ -1620,7 +1620,7 @@
         <v>Goonse</v>
       </c>
       <c r="C62">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F62">
         <v>4</v>
@@ -1629,7 +1629,7 @@
         <v>Goonse</v>
       </c>
       <c r="H62">
-        <v>950</v>
+        <v>1100</v>
       </c>
       <c r="K62">
         <v>4</v>
@@ -1687,7 +1687,7 @@
         <v>Chäli</v>
       </c>
       <c r="C65">
-        <v>2800</v>
+        <v>3200</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -1754,7 +1754,7 @@
         <v>Küng</v>
       </c>
       <c r="C67">
-        <v>1600</v>
+        <v>2300</v>
       </c>
       <c r="F67">
         <v>3</v>
@@ -1985,7 +1985,7 @@
         <v>Küng</v>
       </c>
       <c r="C79">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -1997,7 +1997,7 @@
         <v>Küng</v>
       </c>
       <c r="H79">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I79">
         <v>1</v>
@@ -2006,10 +2006,10 @@
         <v>1</v>
       </c>
       <c r="L79" t="str">
-        <v>Chäli</v>
+        <v>Küng</v>
       </c>
       <c r="M79">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="N79">
         <v>1</v>
@@ -2023,7 +2023,7 @@
         <v>Goonse</v>
       </c>
       <c r="C80">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -2035,7 +2035,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H80">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I80">
         <v>1</v>
@@ -2044,10 +2044,10 @@
         <v>2</v>
       </c>
       <c r="L80" t="str">
-        <v>Küng</v>
+        <v>Chäli</v>
       </c>
       <c r="M80">
-        <v>180</v>
+        <v>240</v>
       </c>
     </row>
     <row r="81">
@@ -2067,7 +2067,7 @@
         <v>Goonse</v>
       </c>
       <c r="H81">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I81">
         <v>1</v>
@@ -2099,7 +2099,7 @@
         <v>Chäli</v>
       </c>
       <c r="H82">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I82">
         <v>1</v>
@@ -2111,7 +2111,7 @@
         <v>Fuchs</v>
       </c>
       <c r="M82">
-        <v>480</v>
+        <v>550</v>
       </c>
     </row>
     <row r="84">
@@ -2157,10 +2157,10 @@
         <v>1</v>
       </c>
       <c r="B85" t="str">
-        <v>Chäli</v>
+        <v>Küng</v>
       </c>
       <c r="C85">
-        <v>14.166667</v>
+        <v>13.846154</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -2169,10 +2169,10 @@
         <v>1</v>
       </c>
       <c r="G85" t="str">
-        <v>Chäli</v>
+        <v>Küng</v>
       </c>
       <c r="H85">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I85">
         <v>1</v>
@@ -2195,19 +2195,19 @@
         <v>2</v>
       </c>
       <c r="B86" t="str">
-        <v>Küng</v>
+        <v>Chäli</v>
       </c>
       <c r="C86">
-        <v>15</v>
+        <v>18.461538</v>
       </c>
       <c r="F86">
         <v>2</v>
       </c>
       <c r="G86" t="str">
-        <v>Küng</v>
+        <v>Chäli</v>
       </c>
       <c r="H86">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K86">
         <v>2</v>
@@ -2216,7 +2216,7 @@
         <v>Küng</v>
       </c>
       <c r="M86">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87">
@@ -2227,7 +2227,7 @@
         <v>Goonse</v>
       </c>
       <c r="C87">
-        <v>29.166667</v>
+        <v>26.923077</v>
       </c>
       <c r="F87">
         <v>3</v>
@@ -2236,16 +2236,16 @@
         <v>Goonse</v>
       </c>
       <c r="H87">
+        <v>16</v>
+      </c>
+      <c r="K87">
+        <v>2</v>
+      </c>
+      <c r="L87" t="str">
+        <v>Fuchs</v>
+      </c>
+      <c r="M87">
         <v>14</v>
-      </c>
-      <c r="K87">
-        <v>3</v>
-      </c>
-      <c r="L87" t="str">
-        <v>Fuchs</v>
-      </c>
-      <c r="M87">
-        <v>12</v>
       </c>
     </row>
     <row r="88">
@@ -2256,7 +2256,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C88">
-        <v>40</v>
+        <v>42.307692</v>
       </c>
       <c r="F88">
         <v>4</v>
@@ -2274,7 +2274,7 @@
         <v>Goonse</v>
       </c>
       <c r="M88">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="94">
@@ -2302,7 +2302,7 @@
         <v>Fuchs</v>
       </c>
       <c r="M95">
-        <v>0.25</v>
+        <v>0.23076923076923078</v>
       </c>
       <c r="N95">
         <v>3</v>
@@ -2311,7 +2311,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="P95">
-        <v>0.08333333333333333</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="96">
@@ -2322,16 +2322,16 @@
         <v>Goonse</v>
       </c>
       <c r="M96">
-        <v>0.4166666666666667</v>
+        <v>0.46153846153846156</v>
       </c>
       <c r="N96">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O96">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="P96">
-        <v>0.3333333333333333</v>
+        <v>0.38461538461538464</v>
       </c>
     </row>
     <row r="97">
@@ -2342,7 +2342,7 @@
         <v>Chäli</v>
       </c>
       <c r="M97">
-        <v>0.3333333333333333</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="N97">
         <v>4</v>
@@ -2351,7 +2351,7 @@
         <v>0.75</v>
       </c>
       <c r="P97">
-        <v>0.25</v>
+        <v>0.23076923076923078</v>
       </c>
     </row>
     <row r="98">
@@ -2362,7 +2362,7 @@
         <v>Goonse</v>
       </c>
       <c r="M98">
-        <v>0.3333333333333333</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="N98">
         <v>4</v>
@@ -2371,7 +2371,7 @@
         <v>0.25</v>
       </c>
       <c r="P98">
-        <v>0.08333333333333333</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="99">
@@ -2382,16 +2382,16 @@
         <v>Chäli</v>
       </c>
       <c r="M99">
-        <v>0.4166666666666667</v>
+        <v>0.46153846153846156</v>
       </c>
       <c r="N99">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O99">
-        <v>0.2</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="P99">
-        <v>0.08333333333333333</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="100">
@@ -2402,7 +2402,7 @@
         <v>Chäli</v>
       </c>
       <c r="M100">
-        <v>0.25</v>
+        <v>0.23076923076923078</v>
       </c>
       <c r="N100">
         <v>3</v>
@@ -2411,7 +2411,7 @@
         <v>1</v>
       </c>
       <c r="P100">
-        <v>0.25</v>
+        <v>0.23076923076923078</v>
       </c>
     </row>
     <row r="110">
@@ -2433,10 +2433,10 @@
         <v>1</v>
       </c>
       <c r="B111" t="str">
-        <v>Chäli</v>
+        <v>Küng</v>
       </c>
       <c r="C111">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="112">
@@ -2444,10 +2444,10 @@
         <v>2</v>
       </c>
       <c r="B112" t="str">
-        <v>Küng</v>
+        <v>Chäli</v>
       </c>
       <c r="C112">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="113">
@@ -2514,6 +2514,9 @@
       <c r="M122">
         <v>12</v>
       </c>
+      <c r="N122">
+        <v>13</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -2555,6 +2558,9 @@
       <c r="M123">
         <v>1</v>
       </c>
+      <c r="N123">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -2596,6 +2602,9 @@
       <c r="M124">
         <v>-1</v>
       </c>
+      <c r="N124">
+        <v>-1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -2637,6 +2646,9 @@
       <c r="M125">
         <v>-1</v>
       </c>
+      <c r="N125">
+        <v>1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -2677,6 +2689,9 @@
       </c>
       <c r="M126">
         <v>1</v>
+      </c>
+      <c r="N126">
+        <v>-1</v>
       </c>
     </row>
     <row r="129">
@@ -2721,6 +2736,9 @@
       <c r="M131" t="str">
         <v>07.09.</v>
       </c>
+      <c r="N131" t="str">
+        <v>14.09.</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -2762,6 +2780,9 @@
       <c r="M132">
         <v>9</v>
       </c>
+      <c r="N132">
+        <v>18</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -2803,6 +2824,9 @@
       <c r="M133">
         <v>1</v>
       </c>
+      <c r="N133">
+        <v>1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -2844,6 +2868,9 @@
       <c r="M134">
         <v>3</v>
       </c>
+      <c r="N134">
+        <v>3</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -2884,6 +2911,9 @@
       </c>
       <c r="M135">
         <v>23</v>
+      </c>
+      <c r="N135">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Statistik_Jassen.xlsx
+++ b/Statistik_Jassen.xlsx
@@ -897,7 +897,7 @@
         <v>Chäli</v>
       </c>
       <c r="C32">
-        <v>107710</v>
+        <v>107701</v>
       </c>
       <c r="F32">
         <v>2</v>
@@ -906,7 +906,7 @@
         <v>Chäli</v>
       </c>
       <c r="H32">
-        <v>8285.384615</v>
+        <v>8284.692308</v>
       </c>
       <c r="K32">
         <v>2</v>
@@ -915,7 +915,7 @@
         <v>Chäli</v>
       </c>
       <c r="M32">
-        <v>2991.944444</v>
+        <v>2991.694444</v>
       </c>
     </row>
     <row r="33">
@@ -955,7 +955,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C34">
-        <v>101139</v>
+        <v>101130</v>
       </c>
       <c r="F34">
         <v>4</v>
@@ -964,7 +964,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H34">
-        <v>7779.923077</v>
+        <v>7779.230769</v>
       </c>
       <c r="K34">
         <v>4</v>
@@ -973,7 +973,7 @@
         <v>Fuchs</v>
       </c>
       <c r="M34">
-        <v>2809.416667</v>
+        <v>2809.166667</v>
       </c>
     </row>
     <row r="36">

--- a/Statistik_Jassen.xlsx
+++ b/Statistik_Jassen.xlsx
@@ -897,7 +897,7 @@
         <v>Chäli</v>
       </c>
       <c r="C32">
-        <v>107701</v>
+        <v>107760</v>
       </c>
       <c r="F32">
         <v>2</v>
@@ -906,7 +906,7 @@
         <v>Chäli</v>
       </c>
       <c r="H32">
-        <v>8284.692308</v>
+        <v>8289.230769</v>
       </c>
       <c r="K32">
         <v>2</v>
@@ -915,7 +915,7 @@
         <v>Chäli</v>
       </c>
       <c r="M32">
-        <v>2991.694444</v>
+        <v>2993.333333</v>
       </c>
     </row>
     <row r="33">
@@ -955,7 +955,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C34">
-        <v>101130</v>
+        <v>101189</v>
       </c>
       <c r="F34">
         <v>4</v>
@@ -964,7 +964,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H34">
-        <v>7779.230769</v>
+        <v>7783.769231</v>
       </c>
       <c r="K34">
         <v>4</v>
@@ -973,7 +973,7 @@
         <v>Fuchs</v>
       </c>
       <c r="M34">
-        <v>2809.166667</v>
+        <v>2810.805556</v>
       </c>
     </row>
     <row r="36">

--- a/Statistik_Jassen.xlsx
+++ b/Statistik_Jassen.xlsx
@@ -432,10 +432,10 @@
         <v>Küng</v>
       </c>
       <c r="H8">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I8">
-        <v>0.3333333333333333</v>
+        <v>0.35353535353535354</v>
       </c>
     </row>
     <row r="9">
@@ -446,10 +446,10 @@
         <v>Chäli</v>
       </c>
       <c r="H9">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I9">
-        <v>0.2777777777777778</v>
+        <v>0.28125</v>
       </c>
     </row>
     <row r="10">
@@ -460,10 +460,10 @@
         <v>Goonse</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>0.2765957446808511</v>
+        <v>0.26732673267326734</v>
       </c>
     </row>
     <row r="11">
@@ -477,7 +477,7 @@
         <v>1</v>
       </c>
       <c r="I11">
-        <v>0.3163265306122449</v>
+        <v>0.33653846153846156</v>
       </c>
     </row>
     <row r="14">
@@ -531,7 +531,7 @@
         <v>Küng</v>
       </c>
       <c r="C17">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -540,7 +540,7 @@
         <v>1</v>
       </c>
       <c r="G17" t="str">
-        <v>Goonse</v>
+        <v>Küng</v>
       </c>
       <c r="H17">
         <v>22</v>
@@ -555,7 +555,7 @@
         <v>Küng</v>
       </c>
       <c r="M17">
-        <v>6.692308</v>
+        <v>6.714286</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -572,13 +572,16 @@
         <v>81</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" t="str">
-        <v>Küng</v>
+        <v>Goonse</v>
       </c>
       <c r="H18">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
       </c>
       <c r="K18">
         <v>2</v>
@@ -587,7 +590,7 @@
         <v>Chäli</v>
       </c>
       <c r="M18">
-        <v>6.230769</v>
+        <v>5.785714</v>
       </c>
     </row>
     <row r="19">
@@ -616,7 +619,7 @@
         <v>Goonse</v>
       </c>
       <c r="M19">
-        <v>5.384615</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -627,7 +630,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C20">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F20">
         <v>4</v>
@@ -636,7 +639,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H20">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K20">
         <v>4</v>
@@ -645,7 +648,7 @@
         <v>Fuchs</v>
       </c>
       <c r="M20">
-        <v>3.846154</v>
+        <v>4.071429</v>
       </c>
     </row>
     <row r="22">
@@ -694,7 +697,7 @@
         <v>Küng</v>
       </c>
       <c r="C23">
-        <v>2.416667</v>
+        <v>2.473684</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -729,7 +732,7 @@
         <v>Chäli</v>
       </c>
       <c r="C24">
-        <v>2.25</v>
+        <v>2.131579</v>
       </c>
       <c r="F24">
         <v>2</v>
@@ -758,7 +761,7 @@
         <v>Goonse</v>
       </c>
       <c r="C25">
-        <v>1.944444</v>
+        <v>1.842105</v>
       </c>
       <c r="F25">
         <v>2</v>
@@ -787,7 +790,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C26">
-        <v>1.388889</v>
+        <v>1.5</v>
       </c>
       <c r="F26">
         <v>4</v>
@@ -859,7 +862,7 @@
         <v>Küng</v>
       </c>
       <c r="C31">
-        <v>108906</v>
+        <v>115451</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -871,7 +874,7 @@
         <v>Küng</v>
       </c>
       <c r="H31">
-        <v>8377.384615</v>
+        <v>8246.5</v>
       </c>
       <c r="I31">
         <v>1</v>
@@ -883,7 +886,7 @@
         <v>Küng</v>
       </c>
       <c r="M31">
-        <v>3025.166667</v>
+        <v>3038.184211</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -897,7 +900,7 @@
         <v>Chäli</v>
       </c>
       <c r="C32">
-        <v>107760</v>
+        <v>113509</v>
       </c>
       <c r="F32">
         <v>2</v>
@@ -906,7 +909,7 @@
         <v>Chäli</v>
       </c>
       <c r="H32">
-        <v>8289.230769</v>
+        <v>8107.785714</v>
       </c>
       <c r="K32">
         <v>2</v>
@@ -915,7 +918,7 @@
         <v>Chäli</v>
       </c>
       <c r="M32">
-        <v>2993.333333</v>
+        <v>2987.078947</v>
       </c>
     </row>
     <row r="33">
@@ -926,7 +929,7 @@
         <v>Goonse</v>
       </c>
       <c r="C33">
-        <v>103639</v>
+        <v>109388</v>
       </c>
       <c r="F33">
         <v>3</v>
@@ -935,7 +938,7 @@
         <v>Goonse</v>
       </c>
       <c r="H33">
-        <v>7972.230769</v>
+        <v>7813.428571</v>
       </c>
       <c r="K33">
         <v>3</v>
@@ -944,7 +947,7 @@
         <v>Goonse</v>
       </c>
       <c r="M33">
-        <v>2878.861111</v>
+        <v>2878.631579</v>
       </c>
     </row>
     <row r="34">
@@ -955,7 +958,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C34">
-        <v>101189</v>
+        <v>107734</v>
       </c>
       <c r="F34">
         <v>4</v>
@@ -964,7 +967,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H34">
-        <v>7783.769231</v>
+        <v>7695.285714</v>
       </c>
       <c r="K34">
         <v>4</v>
@@ -973,7 +976,7 @@
         <v>Fuchs</v>
       </c>
       <c r="M34">
-        <v>2810.805556</v>
+        <v>2835.105263</v>
       </c>
     </row>
     <row r="36">
@@ -1027,7 +1030,7 @@
         <v>Küng</v>
       </c>
       <c r="C39">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1039,7 +1042,7 @@
         <v>Küng</v>
       </c>
       <c r="H39">
-        <v>16448</v>
+        <v>16705</v>
       </c>
       <c r="I39">
         <v>1</v>
@@ -1051,7 +1054,7 @@
         <v>Küng</v>
       </c>
       <c r="M39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N39">
         <v>1</v>
@@ -1077,15 +1080,12 @@
         <v>14906</v>
       </c>
       <c r="K40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L40" t="str">
-        <v>Chäli</v>
+        <v>Fuchs</v>
       </c>
       <c r="M40">
-        <v>1</v>
-      </c>
-      <c r="N40">
         <v>1</v>
       </c>
     </row>
@@ -1109,13 +1109,13 @@
         <v>12336</v>
       </c>
       <c r="K41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L41" t="str">
-        <v>Fuchs</v>
+        <v>Chäli</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1126,7 +1126,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C42">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F42">
         <v>4</v>
@@ -1135,10 +1135,10 @@
         <v>Fuchs</v>
       </c>
       <c r="H42">
-        <v>8738</v>
+        <v>8995</v>
       </c>
       <c r="K42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L42" t="str">
         <v>Goonse</v>
@@ -1361,7 +1361,7 @@
         <v>Chäli</v>
       </c>
       <c r="C53">
-        <v>10870</v>
+        <v>11230</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -1373,7 +1373,7 @@
         <v>Chäli</v>
       </c>
       <c r="H53">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I53">
         <v>1</v>
@@ -1382,10 +1382,10 @@
         <v>1</v>
       </c>
       <c r="L53" t="str">
-        <v>Chäli</v>
+        <v>Küng</v>
       </c>
       <c r="M53">
-        <v>4220</v>
+        <v>4620</v>
       </c>
       <c r="N53">
         <v>1</v>
@@ -1399,7 +1399,7 @@
         <v>Küng</v>
       </c>
       <c r="C54">
-        <v>9440</v>
+        <v>10020</v>
       </c>
       <c r="F54">
         <v>2</v>
@@ -1408,16 +1408,16 @@
         <v>Küng</v>
       </c>
       <c r="H54">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K54">
         <v>2</v>
       </c>
       <c r="L54" t="str">
-        <v>Küng</v>
+        <v>Chäli</v>
       </c>
       <c r="M54">
-        <v>4040</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="55">
@@ -1428,7 +1428,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C55">
-        <v>8050</v>
+        <v>8340</v>
       </c>
       <c r="F55">
         <v>3</v>
@@ -1437,7 +1437,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H55">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K55">
         <v>3</v>
@@ -1446,7 +1446,7 @@
         <v>Fuchs</v>
       </c>
       <c r="M55">
-        <v>3900</v>
+        <v>4040</v>
       </c>
     </row>
     <row r="56">
@@ -1457,7 +1457,7 @@
         <v>Goonse</v>
       </c>
       <c r="C56">
-        <v>6340</v>
+        <v>6760</v>
       </c>
       <c r="F56">
         <v>4</v>
@@ -1466,7 +1466,7 @@
         <v>Goonse</v>
       </c>
       <c r="H56">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="K56">
         <v>4</v>
@@ -1475,7 +1475,7 @@
         <v>Goonse</v>
       </c>
       <c r="M56">
-        <v>3240</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="58">
@@ -1524,7 +1524,7 @@
         <v>Chäli</v>
       </c>
       <c r="C59">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -1536,7 +1536,7 @@
         <v>Chäli</v>
       </c>
       <c r="H59">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="I59">
         <v>1</v>
@@ -1562,7 +1562,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C60">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F60">
         <v>2</v>
@@ -1571,7 +1571,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H60">
-        <v>1650</v>
+        <v>1800</v>
       </c>
       <c r="K60">
         <v>2</v>
@@ -1614,13 +1614,13 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B62" t="str">
         <v>Goonse</v>
       </c>
       <c r="C62">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F62">
         <v>4</v>
@@ -1629,7 +1629,7 @@
         <v>Goonse</v>
       </c>
       <c r="H62">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="K62">
         <v>4</v>
@@ -1985,7 +1985,7 @@
         <v>Küng</v>
       </c>
       <c r="C79">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -1997,7 +1997,7 @@
         <v>Küng</v>
       </c>
       <c r="H79">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I79">
         <v>1</v>
@@ -2017,7 +2017,7 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B80" t="str">
         <v>Goonse</v>
@@ -2025,9 +2025,6 @@
       <c r="C80">
         <v>9</v>
       </c>
-      <c r="D80">
-        <v>1</v>
-      </c>
       <c r="F80">
         <v>1</v>
       </c>
@@ -2035,7 +2032,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H80">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I80">
         <v>1</v>
@@ -2047,7 +2044,7 @@
         <v>Chäli</v>
       </c>
       <c r="M80">
-        <v>240</v>
+        <v>310</v>
       </c>
     </row>
     <row r="81">
@@ -2067,7 +2064,7 @@
         <v>Goonse</v>
       </c>
       <c r="H81">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I81">
         <v>1</v>
@@ -2079,7 +2076,7 @@
         <v>Goonse</v>
       </c>
       <c r="M81">
-        <v>350</v>
+        <v>420</v>
       </c>
     </row>
     <row r="82">
@@ -2090,7 +2087,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C82">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82">
         <v>1</v>
@@ -2099,7 +2096,7 @@
         <v>Chäli</v>
       </c>
       <c r="H82">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I82">
         <v>1</v>
@@ -2160,7 +2157,7 @@
         <v>Küng</v>
       </c>
       <c r="C85">
-        <v>13.846154</v>
+        <v>12.857143</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -2172,7 +2169,7 @@
         <v>Küng</v>
       </c>
       <c r="H85">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I85">
         <v>1</v>
@@ -2198,7 +2195,7 @@
         <v>Chäli</v>
       </c>
       <c r="C86">
-        <v>18.461538</v>
+        <v>22.142857</v>
       </c>
       <c r="F86">
         <v>2</v>
@@ -2227,7 +2224,7 @@
         <v>Goonse</v>
       </c>
       <c r="C87">
-        <v>26.923077</v>
+        <v>30</v>
       </c>
       <c r="F87">
         <v>3</v>
@@ -2256,7 +2253,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C88">
-        <v>42.307692</v>
+        <v>39.285714</v>
       </c>
       <c r="F88">
         <v>4</v>
@@ -2265,7 +2262,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H88">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K88">
         <v>4</v>
@@ -2302,16 +2299,16 @@
         <v>Fuchs</v>
       </c>
       <c r="M95">
-        <v>0.23076923076923078</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="N95">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O95">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="P95">
-        <v>0.07692307692307693</v>
+        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="96">
@@ -2322,7 +2319,7 @@
         <v>Goonse</v>
       </c>
       <c r="M96">
-        <v>0.46153846153846156</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="N96">
         <v>6</v>
@@ -2331,7 +2328,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="P96">
-        <v>0.38461538461538464</v>
+        <v>0.35714285714285715</v>
       </c>
     </row>
     <row r="97">
@@ -2342,7 +2339,7 @@
         <v>Chäli</v>
       </c>
       <c r="M97">
-        <v>0.3076923076923077</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="N97">
         <v>4</v>
@@ -2351,7 +2348,7 @@
         <v>0.75</v>
       </c>
       <c r="P97">
-        <v>0.23076923076923078</v>
+        <v>0.21428571428571427</v>
       </c>
     </row>
     <row r="98">
@@ -2362,7 +2359,7 @@
         <v>Goonse</v>
       </c>
       <c r="M98">
-        <v>0.3076923076923077</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="N98">
         <v>4</v>
@@ -2371,7 +2368,7 @@
         <v>0.25</v>
       </c>
       <c r="P98">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="99">
@@ -2382,7 +2379,7 @@
         <v>Chäli</v>
       </c>
       <c r="M99">
-        <v>0.46153846153846156</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="N99">
         <v>6</v>
@@ -2391,7 +2388,7 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="P99">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="100">
@@ -2402,16 +2399,16 @@
         <v>Chäli</v>
       </c>
       <c r="M100">
-        <v>0.23076923076923078</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="N100">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O100">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="P100">
-        <v>0.23076923076923078</v>
+        <v>0.21428571428571427</v>
       </c>
     </row>
     <row r="110">
@@ -2436,7 +2433,7 @@
         <v>Küng</v>
       </c>
       <c r="C111">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="112">
@@ -2447,7 +2444,7 @@
         <v>Chäli</v>
       </c>
       <c r="C112">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113">
@@ -2458,7 +2455,7 @@
         <v>Goonse</v>
       </c>
       <c r="C113">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
@@ -2517,6 +2514,9 @@
       <c r="N122">
         <v>13</v>
       </c>
+      <c r="O122">
+        <v>14</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -2561,6 +2561,9 @@
       <c r="N123">
         <v>1</v>
       </c>
+      <c r="O123">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -2605,6 +2608,9 @@
       <c r="N124">
         <v>-1</v>
       </c>
+      <c r="O124">
+        <v>1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -2649,6 +2655,9 @@
       <c r="N125">
         <v>1</v>
       </c>
+      <c r="O125">
+        <v>-1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -2691,6 +2700,9 @@
         <v>1</v>
       </c>
       <c r="N126">
+        <v>-1</v>
+      </c>
+      <c r="O126">
         <v>-1</v>
       </c>
     </row>
@@ -2739,6 +2751,9 @@
       <c r="N131" t="str">
         <v>14.09.</v>
       </c>
+      <c r="O131" t="str">
+        <v>21.09.</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -2783,6 +2798,9 @@
       <c r="N132">
         <v>18</v>
       </c>
+      <c r="O132">
+        <v>20</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -2827,6 +2845,9 @@
       <c r="N133">
         <v>1</v>
       </c>
+      <c r="O133">
+        <v>1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -2871,6 +2892,9 @@
       <c r="N134">
         <v>3</v>
       </c>
+      <c r="O134">
+        <v>2</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -2914,6 +2938,9 @@
       </c>
       <c r="N135">
         <v>14</v>
+      </c>
+      <c r="O135">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Statistik_Jassen.xlsx
+++ b/Statistik_Jassen.xlsx
@@ -432,10 +432,10 @@
         <v>Küng</v>
       </c>
       <c r="H8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I8">
-        <v>0.35353535353535354</v>
+        <v>0.34579439252336447</v>
       </c>
     </row>
     <row r="9">
@@ -446,10 +446,10 @@
         <v>Chäli</v>
       </c>
       <c r="H9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I9">
-        <v>0.28125</v>
+        <v>0.27884615384615385</v>
       </c>
     </row>
     <row r="10">
@@ -457,27 +457,27 @@
         <v>3</v>
       </c>
       <c r="G10" t="str">
-        <v>Goonse</v>
+        <v>Fuchs</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>0.26732673267326734</v>
+        <v>0.3392857142857143</v>
       </c>
     </row>
     <row r="11">
       <c r="F11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" t="str">
-        <v>Fuchs</v>
+        <v>Goonse</v>
       </c>
       <c r="H11">
         <v>1</v>
       </c>
       <c r="I11">
-        <v>0.33653846153846156</v>
+        <v>0.25925925925925924</v>
       </c>
     </row>
     <row r="14">
@@ -531,7 +531,7 @@
         <v>Küng</v>
       </c>
       <c r="C17">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -543,7 +543,7 @@
         <v>Küng</v>
       </c>
       <c r="H17">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I17">
         <v>1</v>
@@ -555,7 +555,7 @@
         <v>Küng</v>
       </c>
       <c r="M17">
-        <v>6.714286</v>
+        <v>6.666667</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -569,19 +569,16 @@
         <v>Chäli</v>
       </c>
       <c r="C18">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" t="str">
         <v>Goonse</v>
       </c>
       <c r="H18">
-        <v>22</v>
-      </c>
-      <c r="I18">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="K18">
         <v>2</v>
@@ -590,7 +587,7 @@
         <v>Chäli</v>
       </c>
       <c r="M18">
-        <v>5.785714</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="19">
@@ -601,7 +598,7 @@
         <v>Goonse</v>
       </c>
       <c r="C19">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F19">
         <v>3</v>
@@ -610,7 +607,7 @@
         <v>Chäli</v>
       </c>
       <c r="H19">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K19">
         <v>3</v>
@@ -619,7 +616,7 @@
         <v>Goonse</v>
       </c>
       <c r="M19">
-        <v>5</v>
+        <v>4.866667</v>
       </c>
     </row>
     <row r="20">
@@ -630,7 +627,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C20">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F20">
         <v>4</v>
@@ -639,7 +636,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H20">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K20">
         <v>4</v>
@@ -648,7 +645,7 @@
         <v>Fuchs</v>
       </c>
       <c r="M20">
-        <v>4.071429</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -697,7 +694,7 @@
         <v>Küng</v>
       </c>
       <c r="C23">
-        <v>2.473684</v>
+        <v>2.439024</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -732,7 +729,7 @@
         <v>Chäli</v>
       </c>
       <c r="C24">
-        <v>2.131579</v>
+        <v>2.121951</v>
       </c>
       <c r="F24">
         <v>2</v>
@@ -761,7 +758,7 @@
         <v>Goonse</v>
       </c>
       <c r="C25">
-        <v>1.842105</v>
+        <v>1.780488</v>
       </c>
       <c r="F25">
         <v>2</v>
@@ -790,7 +787,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C26">
-        <v>1.5</v>
+        <v>1.463415</v>
       </c>
       <c r="F26">
         <v>4</v>
@@ -862,7 +859,7 @@
         <v>Küng</v>
       </c>
       <c r="C31">
-        <v>115451</v>
+        <v>124658</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -874,7 +871,7 @@
         <v>Küng</v>
       </c>
       <c r="H31">
-        <v>8246.5</v>
+        <v>8310.533333</v>
       </c>
       <c r="I31">
         <v>1</v>
@@ -886,7 +883,7 @@
         <v>Küng</v>
       </c>
       <c r="M31">
-        <v>3038.184211</v>
+        <v>3040.439024</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -900,7 +897,7 @@
         <v>Chäli</v>
       </c>
       <c r="C32">
-        <v>113509</v>
+        <v>122716</v>
       </c>
       <c r="F32">
         <v>2</v>
@@ -909,7 +906,7 @@
         <v>Chäli</v>
       </c>
       <c r="H32">
-        <v>8107.785714</v>
+        <v>8181.066667</v>
       </c>
       <c r="K32">
         <v>2</v>
@@ -918,7 +915,7 @@
         <v>Chäli</v>
       </c>
       <c r="M32">
-        <v>2987.078947</v>
+        <v>2993.073171</v>
       </c>
     </row>
     <row r="33">
@@ -929,7 +926,7 @@
         <v>Goonse</v>
       </c>
       <c r="C33">
-        <v>109388</v>
+        <v>117627</v>
       </c>
       <c r="F33">
         <v>3</v>
@@ -938,7 +935,7 @@
         <v>Goonse</v>
       </c>
       <c r="H33">
-        <v>7813.428571</v>
+        <v>7841.8</v>
       </c>
       <c r="K33">
         <v>3</v>
@@ -947,7 +944,7 @@
         <v>Goonse</v>
       </c>
       <c r="M33">
-        <v>2878.631579</v>
+        <v>2868.95122</v>
       </c>
     </row>
     <row r="34">
@@ -958,7 +955,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C34">
-        <v>107734</v>
+        <v>115973</v>
       </c>
       <c r="F34">
         <v>4</v>
@@ -967,7 +964,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H34">
-        <v>7695.285714</v>
+        <v>7731.533333</v>
       </c>
       <c r="K34">
         <v>4</v>
@@ -976,7 +973,7 @@
         <v>Fuchs</v>
       </c>
       <c r="M34">
-        <v>2835.105263</v>
+        <v>2828.609756</v>
       </c>
     </row>
     <row r="36">
@@ -1361,7 +1358,7 @@
         <v>Chäli</v>
       </c>
       <c r="C53">
-        <v>11230</v>
+        <v>12390</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -1373,7 +1370,7 @@
         <v>Chäli</v>
       </c>
       <c r="H53">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="I53">
         <v>1</v>
@@ -1382,10 +1379,10 @@
         <v>1</v>
       </c>
       <c r="L53" t="str">
-        <v>Küng</v>
+        <v>Chäli</v>
       </c>
       <c r="M53">
-        <v>4620</v>
+        <v>4940</v>
       </c>
       <c r="N53">
         <v>1</v>
@@ -1399,7 +1396,7 @@
         <v>Küng</v>
       </c>
       <c r="C54">
-        <v>10020</v>
+        <v>10320</v>
       </c>
       <c r="F54">
         <v>2</v>
@@ -1408,16 +1405,16 @@
         <v>Küng</v>
       </c>
       <c r="H54">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="K54">
         <v>2</v>
       </c>
       <c r="L54" t="str">
-        <v>Chäli</v>
+        <v>Küng</v>
       </c>
       <c r="M54">
-        <v>4480</v>
+        <v>4920</v>
       </c>
     </row>
     <row r="55">
@@ -1428,7 +1425,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C55">
-        <v>8340</v>
+        <v>9330</v>
       </c>
       <c r="F55">
         <v>3</v>
@@ -1437,7 +1434,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H55">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K55">
         <v>3</v>
@@ -1446,7 +1443,7 @@
         <v>Fuchs</v>
       </c>
       <c r="M55">
-        <v>4040</v>
+        <v>4380</v>
       </c>
     </row>
     <row r="56">
@@ -1457,7 +1454,7 @@
         <v>Goonse</v>
       </c>
       <c r="C56">
-        <v>6760</v>
+        <v>7220</v>
       </c>
       <c r="F56">
         <v>4</v>
@@ -1466,7 +1463,7 @@
         <v>Goonse</v>
       </c>
       <c r="H56">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="K56">
         <v>4</v>
@@ -1475,7 +1472,7 @@
         <v>Goonse</v>
       </c>
       <c r="M56">
-        <v>3560</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="58">
@@ -1524,7 +1521,7 @@
         <v>Chäli</v>
       </c>
       <c r="C59">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -1536,7 +1533,7 @@
         <v>Chäli</v>
       </c>
       <c r="H59">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="I59">
         <v>1</v>
@@ -1562,7 +1559,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C60">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F60">
         <v>2</v>
@@ -1571,7 +1568,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H60">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="K60">
         <v>2</v>
@@ -1588,10 +1585,10 @@
         <v>3</v>
       </c>
       <c r="B61" t="str">
-        <v>Küng</v>
+        <v>Goonse</v>
       </c>
       <c r="C61">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F61">
         <v>3</v>
@@ -1614,10 +1611,10 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B62" t="str">
-        <v>Goonse</v>
+        <v>Küng</v>
       </c>
       <c r="C62">
         <v>10</v>
@@ -1629,7 +1626,7 @@
         <v>Goonse</v>
       </c>
       <c r="H62">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="K62">
         <v>4</v>
@@ -1699,7 +1696,7 @@
         <v>Chäli</v>
       </c>
       <c r="H65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I65">
         <v>1</v>
@@ -1711,7 +1708,7 @@
         <v>Chäli</v>
       </c>
       <c r="M65">
-        <v>1350</v>
+        <v>1950</v>
       </c>
       <c r="N65">
         <v>1</v>
@@ -1731,7 +1728,7 @@
         <v>2</v>
       </c>
       <c r="G66" t="str">
-        <v>Goonse</v>
+        <v>Fuchs</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -1757,22 +1754,22 @@
         <v>2300</v>
       </c>
       <c r="F67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G67" t="str">
-        <v>Küng</v>
+        <v>Goonse</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67">
         <v>3</v>
       </c>
       <c r="L67" t="str">
-        <v>Küng</v>
+        <v>Fuchs</v>
       </c>
       <c r="M67">
-        <v>0</v>
+        <v>450</v>
       </c>
     </row>
     <row r="68">
@@ -1786,19 +1783,19 @@
         <v>800</v>
       </c>
       <c r="F68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="str">
-        <v>Fuchs</v>
+        <v>Küng</v>
       </c>
       <c r="H68">
         <v>0</v>
       </c>
       <c r="K68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L68" t="str">
-        <v>Fuchs</v>
+        <v>Küng</v>
       </c>
       <c r="M68">
         <v>0</v>
@@ -1985,7 +1982,7 @@
         <v>Küng</v>
       </c>
       <c r="C79">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -1997,7 +1994,7 @@
         <v>Küng</v>
       </c>
       <c r="H79">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I79">
         <v>1</v>
@@ -2032,7 +2029,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H80">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I80">
         <v>1</v>
@@ -2055,7 +2052,7 @@
         <v>Chäli</v>
       </c>
       <c r="C81">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F81">
         <v>1</v>
@@ -2064,7 +2061,7 @@
         <v>Goonse</v>
       </c>
       <c r="H81">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I81">
         <v>1</v>
@@ -2076,7 +2073,7 @@
         <v>Goonse</v>
       </c>
       <c r="M81">
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row r="82">
@@ -2096,7 +2093,7 @@
         <v>Chäli</v>
       </c>
       <c r="H82">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I82">
         <v>1</v>
@@ -2108,7 +2105,7 @@
         <v>Fuchs</v>
       </c>
       <c r="M82">
-        <v>550</v>
+        <v>580</v>
       </c>
     </row>
     <row r="84">
@@ -2157,7 +2154,7 @@
         <v>Küng</v>
       </c>
       <c r="C85">
-        <v>12.857143</v>
+        <v>12</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -2169,7 +2166,7 @@
         <v>Küng</v>
       </c>
       <c r="H85">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I85">
         <v>1</v>
@@ -2181,7 +2178,7 @@
         <v>Chäli</v>
       </c>
       <c r="M85">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N85">
         <v>1</v>
@@ -2195,7 +2192,7 @@
         <v>Chäli</v>
       </c>
       <c r="C86">
-        <v>22.142857</v>
+        <v>20.666667</v>
       </c>
       <c r="F86">
         <v>2</v>
@@ -2204,13 +2201,13 @@
         <v>Chäli</v>
       </c>
       <c r="H86">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K86">
         <v>2</v>
       </c>
       <c r="L86" t="str">
-        <v>Küng</v>
+        <v>Fuchs</v>
       </c>
       <c r="M86">
         <v>14</v>
@@ -2233,16 +2230,16 @@
         <v>Goonse</v>
       </c>
       <c r="H87">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K87">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L87" t="str">
-        <v>Fuchs</v>
+        <v>Küng</v>
       </c>
       <c r="M87">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="88">
@@ -2253,7 +2250,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C88">
-        <v>39.285714</v>
+        <v>38.666667</v>
       </c>
       <c r="F88">
         <v>4</v>
@@ -2262,7 +2259,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H88">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K88">
         <v>4</v>
@@ -2271,7 +2268,7 @@
         <v>Goonse</v>
       </c>
       <c r="M88">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="94">
@@ -2299,7 +2296,7 @@
         <v>Fuchs</v>
       </c>
       <c r="M95">
-        <v>0.2857142857142857</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="N95">
         <v>4</v>
@@ -2308,7 +2305,7 @@
         <v>0.5</v>
       </c>
       <c r="P95">
-        <v>0.14285714285714285</v>
+        <v>0.13333333333333333</v>
       </c>
     </row>
     <row r="96">
@@ -2319,7 +2316,7 @@
         <v>Goonse</v>
       </c>
       <c r="M96">
-        <v>0.42857142857142855</v>
+        <v>0.4</v>
       </c>
       <c r="N96">
         <v>6</v>
@@ -2328,7 +2325,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="P96">
-        <v>0.35714285714285715</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="97">
@@ -2339,16 +2336,16 @@
         <v>Chäli</v>
       </c>
       <c r="M97">
-        <v>0.2857142857142857</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N97">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O97">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="P97">
-        <v>0.21428571428571427</v>
+        <v>0.26666666666666666</v>
       </c>
     </row>
     <row r="98">
@@ -2359,16 +2356,16 @@
         <v>Goonse</v>
       </c>
       <c r="M98">
-        <v>0.2857142857142857</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N98">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O98">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="P98">
-        <v>0.07142857142857142</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="99">
@@ -2379,7 +2376,7 @@
         <v>Chäli</v>
       </c>
       <c r="M99">
-        <v>0.42857142857142855</v>
+        <v>0.4</v>
       </c>
       <c r="N99">
         <v>6</v>
@@ -2388,7 +2385,7 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="P99">
-        <v>0.07142857142857142</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="100">
@@ -2399,7 +2396,7 @@
         <v>Chäli</v>
       </c>
       <c r="M100">
-        <v>0.2857142857142857</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="N100">
         <v>4</v>
@@ -2408,7 +2405,7 @@
         <v>0.75</v>
       </c>
       <c r="P100">
-        <v>0.21428571428571427</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="110">
@@ -2433,7 +2430,7 @@
         <v>Küng</v>
       </c>
       <c r="C111">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112">
@@ -2444,7 +2441,7 @@
         <v>Chäli</v>
       </c>
       <c r="C112">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113">
@@ -2452,18 +2449,18 @@
         <v>3</v>
       </c>
       <c r="B113" t="str">
-        <v>Goonse</v>
+        <v>Fuchs</v>
       </c>
       <c r="C113">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B114" t="str">
-        <v>Fuchs</v>
+        <v>Goonse</v>
       </c>
       <c r="C114">
         <v>1</v>
@@ -2517,6 +2514,9 @@
       <c r="O122">
         <v>14</v>
       </c>
+      <c r="P122">
+        <v>15</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -2564,6 +2564,9 @@
       <c r="O123">
         <v>1</v>
       </c>
+      <c r="P123">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -2611,6 +2614,9 @@
       <c r="O124">
         <v>1</v>
       </c>
+      <c r="P124">
+        <v>-1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -2658,6 +2664,9 @@
       <c r="O125">
         <v>-1</v>
       </c>
+      <c r="P125">
+        <v>-1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -2704,6 +2713,9 @@
       </c>
       <c r="O126">
         <v>-1</v>
+      </c>
+      <c r="P126">
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -2754,6 +2766,9 @@
       <c r="O131" t="str">
         <v>21.09.</v>
       </c>
+      <c r="P131" t="str">
+        <v>28.09.</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -2801,6 +2816,9 @@
       <c r="O132">
         <v>20</v>
       </c>
+      <c r="P132">
+        <v>19</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -2848,6 +2866,9 @@
       <c r="O133">
         <v>1</v>
       </c>
+      <c r="P133">
+        <v>1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -2895,6 +2916,9 @@
       <c r="O134">
         <v>2</v>
       </c>
+      <c r="P134">
+        <v>1</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -2941,6 +2965,9 @@
       </c>
       <c r="O135">
         <v>12</v>
+      </c>
+      <c r="P135">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Statistik_Jassen.xlsx
+++ b/Statistik_Jassen.xlsx
@@ -435,7 +435,7 @@
         <v>19</v>
       </c>
       <c r="I8">
-        <v>0.34579439252336447</v>
+        <v>0.33962264150943394</v>
       </c>
     </row>
     <row r="9">
@@ -477,7 +477,7 @@
         <v>1</v>
       </c>
       <c r="I11">
-        <v>0.25925925925925924</v>
+        <v>0.25688073394495414</v>
       </c>
     </row>
     <row r="14">

--- a/Statistik_Jassen.xlsx
+++ b/Statistik_Jassen.xlsx
@@ -435,7 +435,7 @@
         <v>19</v>
       </c>
       <c r="I8">
-        <v>0.33962264150943394</v>
+        <v>0.3482142857142857</v>
       </c>
     </row>
     <row r="9">
@@ -446,10 +446,10 @@
         <v>Chäli</v>
       </c>
       <c r="H9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I9">
-        <v>0.27884615384615385</v>
+        <v>0.27522935779816515</v>
       </c>
     </row>
     <row r="10">
@@ -457,27 +457,27 @@
         <v>3</v>
       </c>
       <c r="G10" t="str">
-        <v>Fuchs</v>
+        <v>Goonse</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>0.3392857142857143</v>
+        <v>0.2543859649122807</v>
       </c>
     </row>
     <row r="11">
       <c r="F11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" t="str">
-        <v>Goonse</v>
+        <v>Fuchs</v>
       </c>
       <c r="H11">
         <v>1</v>
       </c>
       <c r="I11">
-        <v>0.25688073394495414</v>
+        <v>0.3418803418803419</v>
       </c>
     </row>
     <row r="14">
@@ -531,7 +531,7 @@
         <v>Küng</v>
       </c>
       <c r="C17">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -540,10 +540,10 @@
         <v>1</v>
       </c>
       <c r="G17" t="str">
-        <v>Küng</v>
+        <v>Goonse</v>
       </c>
       <c r="H17">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I17">
         <v>1</v>
@@ -555,7 +555,7 @@
         <v>Küng</v>
       </c>
       <c r="M17">
-        <v>6.666667</v>
+        <v>6.5625</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -569,16 +569,16 @@
         <v>Chäli</v>
       </c>
       <c r="C18">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F18">
         <v>2</v>
       </c>
       <c r="G18" t="str">
-        <v>Goonse</v>
+        <v>Küng</v>
       </c>
       <c r="H18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K18">
         <v>2</v>
@@ -587,7 +587,7 @@
         <v>Chäli</v>
       </c>
       <c r="M18">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="19">
@@ -598,7 +598,7 @@
         <v>Goonse</v>
       </c>
       <c r="C19">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F19">
         <v>3</v>
@@ -616,7 +616,7 @@
         <v>Goonse</v>
       </c>
       <c r="M19">
-        <v>4.866667</v>
+        <v>4.8125</v>
       </c>
     </row>
     <row r="20">
@@ -627,7 +627,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C20">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F20">
         <v>4</v>
@@ -636,7 +636,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H20">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K20">
         <v>4</v>
@@ -694,7 +694,7 @@
         <v>Küng</v>
       </c>
       <c r="C23">
-        <v>2.439024</v>
+        <v>2.44186</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -706,7 +706,7 @@
         <v>Chäli</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23">
         <v>1</v>
@@ -729,7 +729,7 @@
         <v>Chäli</v>
       </c>
       <c r="C24">
-        <v>2.121951</v>
+        <v>2.139535</v>
       </c>
       <c r="F24">
         <v>2</v>
@@ -738,7 +738,7 @@
         <v>Küng</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K24">
         <v>1</v>
@@ -758,10 +758,10 @@
         <v>Goonse</v>
       </c>
       <c r="C25">
-        <v>1.780488</v>
+        <v>1.790698</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" t="str">
         <v>Fuchs</v>
@@ -787,7 +787,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C26">
-        <v>1.463415</v>
+        <v>1.488372</v>
       </c>
       <c r="F26">
         <v>4</v>
@@ -859,7 +859,7 @@
         <v>Küng</v>
       </c>
       <c r="C31">
-        <v>124658</v>
+        <v>130293</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -871,7 +871,7 @@
         <v>Küng</v>
       </c>
       <c r="H31">
-        <v>8310.533333</v>
+        <v>8143.3125</v>
       </c>
       <c r="I31">
         <v>1</v>
@@ -883,7 +883,7 @@
         <v>Küng</v>
       </c>
       <c r="M31">
-        <v>3040.439024</v>
+        <v>3030.069767</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -897,7 +897,7 @@
         <v>Chäli</v>
       </c>
       <c r="C32">
-        <v>122716</v>
+        <v>128351</v>
       </c>
       <c r="F32">
         <v>2</v>
@@ -906,7 +906,7 @@
         <v>Chäli</v>
       </c>
       <c r="H32">
-        <v>8181.066667</v>
+        <v>8021.9375</v>
       </c>
       <c r="K32">
         <v>2</v>
@@ -915,7 +915,7 @@
         <v>Chäli</v>
       </c>
       <c r="M32">
-        <v>2993.073171</v>
+        <v>2984.906977</v>
       </c>
     </row>
     <row r="33">
@@ -926,7 +926,7 @@
         <v>Goonse</v>
       </c>
       <c r="C33">
-        <v>117627</v>
+        <v>122202</v>
       </c>
       <c r="F33">
         <v>3</v>
@@ -935,7 +935,7 @@
         <v>Goonse</v>
       </c>
       <c r="H33">
-        <v>7841.8</v>
+        <v>7637.625</v>
       </c>
       <c r="K33">
         <v>3</v>
@@ -944,7 +944,7 @@
         <v>Goonse</v>
       </c>
       <c r="M33">
-        <v>2868.95122</v>
+        <v>2841.906977</v>
       </c>
     </row>
     <row r="34">
@@ -955,7 +955,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C34">
-        <v>115973</v>
+        <v>120548</v>
       </c>
       <c r="F34">
         <v>4</v>
@@ -964,7 +964,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H34">
-        <v>7731.533333</v>
+        <v>7534.25</v>
       </c>
       <c r="K34">
         <v>4</v>
@@ -973,7 +973,7 @@
         <v>Fuchs</v>
       </c>
       <c r="M34">
-        <v>2828.609756</v>
+        <v>2803.44186</v>
       </c>
     </row>
     <row r="36">
@@ -1027,7 +1027,7 @@
         <v>Küng</v>
       </c>
       <c r="C39">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1039,7 +1039,7 @@
         <v>Küng</v>
       </c>
       <c r="H39">
-        <v>16705</v>
+        <v>17733</v>
       </c>
       <c r="I39">
         <v>1</v>
@@ -1065,7 +1065,7 @@
         <v>Chäli</v>
       </c>
       <c r="C40">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F40">
         <v>2</v>
@@ -1074,7 +1074,7 @@
         <v>Chäli</v>
       </c>
       <c r="H40">
-        <v>14906</v>
+        <v>15934</v>
       </c>
       <c r="K40">
         <v>2</v>
@@ -1190,7 +1190,7 @@
         <v>Küng</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -1225,10 +1225,10 @@
         <v>2</v>
       </c>
       <c r="B46" t="str">
-        <v>Goonse</v>
+        <v>Chäli</v>
       </c>
       <c r="C46">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F46">
         <v>2</v>
@@ -1251,10 +1251,10 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B47" t="str">
-        <v>Chäli</v>
+        <v>Goonse</v>
       </c>
       <c r="C47">
         <v>5</v>
@@ -1358,7 +1358,7 @@
         <v>Chäli</v>
       </c>
       <c r="C53">
-        <v>12390</v>
+        <v>12710</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -1370,7 +1370,7 @@
         <v>Chäli</v>
       </c>
       <c r="H53">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I53">
         <v>1</v>
@@ -1379,10 +1379,10 @@
         <v>1</v>
       </c>
       <c r="L53" t="str">
-        <v>Chäli</v>
+        <v>Küng</v>
       </c>
       <c r="M53">
-        <v>4940</v>
+        <v>5140</v>
       </c>
       <c r="N53">
         <v>1</v>
@@ -1396,7 +1396,7 @@
         <v>Küng</v>
       </c>
       <c r="C54">
-        <v>10320</v>
+        <v>10840</v>
       </c>
       <c r="F54">
         <v>2</v>
@@ -1405,16 +1405,16 @@
         <v>Küng</v>
       </c>
       <c r="H54">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K54">
         <v>2</v>
       </c>
       <c r="L54" t="str">
-        <v>Küng</v>
+        <v>Chäli</v>
       </c>
       <c r="M54">
-        <v>4920</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="55">
@@ -1425,7 +1425,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C55">
-        <v>9330</v>
+        <v>9670</v>
       </c>
       <c r="F55">
         <v>3</v>
@@ -1434,7 +1434,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H55">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="K55">
         <v>3</v>
@@ -1443,7 +1443,7 @@
         <v>Fuchs</v>
       </c>
       <c r="M55">
-        <v>4380</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="56">
@@ -1454,7 +1454,7 @@
         <v>Goonse</v>
       </c>
       <c r="C56">
-        <v>7220</v>
+        <v>7380</v>
       </c>
       <c r="F56">
         <v>4</v>
@@ -1463,7 +1463,7 @@
         <v>Goonse</v>
       </c>
       <c r="H56">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K56">
         <v>4</v>
@@ -1472,7 +1472,7 @@
         <v>Goonse</v>
       </c>
       <c r="M56">
-        <v>3820</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="58">
@@ -1545,7 +1545,7 @@
         <v>Chäli</v>
       </c>
       <c r="M59">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N59">
         <v>1</v>
@@ -1574,7 +1574,7 @@
         <v>2</v>
       </c>
       <c r="L60" t="str">
-        <v>Fuchs</v>
+        <v>Küng</v>
       </c>
       <c r="M60">
         <v>8</v>
@@ -1600,13 +1600,13 @@
         <v>1500</v>
       </c>
       <c r="K61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L61" t="str">
-        <v>Küng</v>
+        <v>Fuchs</v>
       </c>
       <c r="M61">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62">
@@ -1684,7 +1684,7 @@
         <v>Chäli</v>
       </c>
       <c r="C65">
-        <v>3200</v>
+        <v>3400</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -1719,10 +1719,10 @@
         <v>2</v>
       </c>
       <c r="B66" t="str">
-        <v>Fuchs</v>
+        <v>Küng</v>
       </c>
       <c r="C66">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="F66">
         <v>2</v>
@@ -1748,10 +1748,10 @@
         <v>3</v>
       </c>
       <c r="B67" t="str">
-        <v>Küng</v>
+        <v>Fuchs</v>
       </c>
       <c r="C67">
-        <v>2300</v>
+        <v>2500</v>
       </c>
       <c r="F67">
         <v>2</v>
@@ -1982,7 +1982,7 @@
         <v>Küng</v>
       </c>
       <c r="C79">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -1994,7 +1994,7 @@
         <v>Küng</v>
       </c>
       <c r="H79">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I79">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H80">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I80">
         <v>1</v>
@@ -2046,13 +2046,13 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B81" t="str">
         <v>Chäli</v>
       </c>
       <c r="C81">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F81">
         <v>1</v>
@@ -2061,7 +2061,7 @@
         <v>Goonse</v>
       </c>
       <c r="H81">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I81">
         <v>1</v>
@@ -2073,7 +2073,7 @@
         <v>Goonse</v>
       </c>
       <c r="M81">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="82">
@@ -2093,7 +2093,7 @@
         <v>Chäli</v>
       </c>
       <c r="H82">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I82">
         <v>1</v>
@@ -2105,7 +2105,7 @@
         <v>Fuchs</v>
       </c>
       <c r="M82">
-        <v>580</v>
+        <v>590</v>
       </c>
     </row>
     <row r="84">
@@ -2154,7 +2154,7 @@
         <v>Küng</v>
       </c>
       <c r="C85">
-        <v>12</v>
+        <v>11.25</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -2166,7 +2166,7 @@
         <v>Küng</v>
       </c>
       <c r="H85">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I85">
         <v>1</v>
@@ -2192,7 +2192,7 @@
         <v>Chäli</v>
       </c>
       <c r="C86">
-        <v>20.666667</v>
+        <v>19.375</v>
       </c>
       <c r="F86">
         <v>2</v>
@@ -2201,7 +2201,7 @@
         <v>Chäli</v>
       </c>
       <c r="H86">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K86">
         <v>2</v>
@@ -2221,7 +2221,7 @@
         <v>Goonse</v>
       </c>
       <c r="C87">
-        <v>30</v>
+        <v>28.75</v>
       </c>
       <c r="F87">
         <v>3</v>
@@ -2230,7 +2230,7 @@
         <v>Goonse</v>
       </c>
       <c r="H87">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K87">
         <v>3</v>
@@ -2239,7 +2239,7 @@
         <v>Küng</v>
       </c>
       <c r="M87">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="88">
@@ -2250,7 +2250,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C88">
-        <v>38.666667</v>
+        <v>36.875</v>
       </c>
       <c r="F88">
         <v>4</v>
@@ -2259,7 +2259,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H88">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K88">
         <v>4</v>
@@ -2296,7 +2296,7 @@
         <v>Fuchs</v>
       </c>
       <c r="M95">
-        <v>0.26666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="N95">
         <v>4</v>
@@ -2305,7 +2305,7 @@
         <v>0.5</v>
       </c>
       <c r="P95">
-        <v>0.13333333333333333</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="96">
@@ -2316,7 +2316,7 @@
         <v>Goonse</v>
       </c>
       <c r="M96">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="N96">
         <v>6</v>
@@ -2325,7 +2325,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="P96">
-        <v>0.3333333333333333</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="97">
@@ -2336,16 +2336,16 @@
         <v>Chäli</v>
       </c>
       <c r="M97">
-        <v>0.3333333333333333</v>
+        <v>0.375</v>
       </c>
       <c r="N97">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O97">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="P97">
-        <v>0.26666666666666666</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="98">
@@ -2356,16 +2356,16 @@
         <v>Goonse</v>
       </c>
       <c r="M98">
-        <v>0.3333333333333333</v>
+        <v>0.375</v>
       </c>
       <c r="N98">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O98">
-        <v>0.2</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="P98">
-        <v>0.06666666666666667</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="99">
@@ -2376,7 +2376,7 @@
         <v>Chäli</v>
       </c>
       <c r="M99">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="N99">
         <v>6</v>
@@ -2385,7 +2385,7 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="P99">
-        <v>0.06666666666666667</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="100">
@@ -2396,7 +2396,7 @@
         <v>Chäli</v>
       </c>
       <c r="M100">
-        <v>0.26666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="N100">
         <v>4</v>
@@ -2405,7 +2405,7 @@
         <v>0.75</v>
       </c>
       <c r="P100">
-        <v>0.2</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="110">
@@ -2441,7 +2441,7 @@
         <v>Chäli</v>
       </c>
       <c r="C112">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113">
@@ -2449,18 +2449,18 @@
         <v>3</v>
       </c>
       <c r="B113" t="str">
-        <v>Fuchs</v>
+        <v>Goonse</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B114" t="str">
-        <v>Goonse</v>
+        <v>Fuchs</v>
       </c>
       <c r="C114">
         <v>1</v>
@@ -2517,6 +2517,9 @@
       <c r="P122">
         <v>15</v>
       </c>
+      <c r="Q122">
+        <v>16</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -2567,6 +2570,9 @@
       <c r="P123">
         <v>1</v>
       </c>
+      <c r="Q123">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -2617,6 +2623,9 @@
       <c r="P124">
         <v>-1</v>
       </c>
+      <c r="Q124">
+        <v>-1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -2667,6 +2676,9 @@
       <c r="P125">
         <v>-1</v>
       </c>
+      <c r="Q125">
+        <v>-1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -2715,6 +2727,9 @@
         <v>-1</v>
       </c>
       <c r="P126">
+        <v>1</v>
+      </c>
+      <c r="Q126">
         <v>1</v>
       </c>
     </row>
@@ -2769,6 +2784,9 @@
       <c r="P131" t="str">
         <v>28.09.</v>
       </c>
+      <c r="Q131" t="str">
+        <v>26.10.</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -2819,6 +2837,9 @@
       <c r="P132">
         <v>19</v>
       </c>
+      <c r="Q132">
+        <v>19</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -2869,6 +2890,9 @@
       <c r="P133">
         <v>1</v>
       </c>
+      <c r="Q133">
+        <v>1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -2919,6 +2943,9 @@
       <c r="P134">
         <v>1</v>
       </c>
+      <c r="Q134">
+        <v>2</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -2968,6 +2995,9 @@
       </c>
       <c r="P135">
         <v>13</v>
+      </c>
+      <c r="Q135">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Statistik_Jassen.xlsx
+++ b/Statistik_Jassen.xlsx
@@ -457,27 +457,27 @@
         <v>3</v>
       </c>
       <c r="G10" t="str">
-        <v>Goonse</v>
+        <v>Fuchs</v>
       </c>
       <c r="H10">
         <v>2</v>
       </c>
       <c r="I10">
-        <v>0.2543859649122807</v>
+        <v>0.3418803418803419</v>
       </c>
     </row>
     <row r="11">
       <c r="F11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" t="str">
-        <v>Fuchs</v>
+        <v>Goonse</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11">
-        <v>0.3418803418803419</v>
+        <v>0.2543859649122807</v>
       </c>
     </row>
     <row r="14">
@@ -2271,7 +2271,66 @@
         <v>20</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>Ranking</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Spieler</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Total Aufstehen</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Pokal</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>1</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Fuchs</v>
+      </c>
+      <c r="C91">
+        <v>4</v>
+      </c>
+      <c r="D91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>2</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Chäli</v>
+      </c>
+      <c r="C92">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>3</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Küng</v>
+      </c>
+      <c r="C93">
+        <v>7</v>
+      </c>
+    </row>
     <row r="94">
+      <c r="A94">
+        <v>3</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Goonse</v>
+      </c>
+      <c r="C94">
+        <v>7</v>
+      </c>
       <c r="K94" t="str">
         <v>Teamkonstellationen</v>
       </c>
@@ -2449,7 +2508,7 @@
         <v>3</v>
       </c>
       <c r="B113" t="str">
-        <v>Goonse</v>
+        <v>Fuchs</v>
       </c>
       <c r="C113">
         <v>2</v>
@@ -2457,13 +2516,13 @@
     </row>
     <row r="114">
       <c r="A114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B114" t="str">
-        <v>Fuchs</v>
+        <v>Goonse</v>
       </c>
       <c r="C114">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
@@ -2793,28 +2852,28 @@
         <v>Küng</v>
       </c>
       <c r="B132">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D132">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E132">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F132">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G132">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H132">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I132">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J132">
         <v>9</v>
@@ -2846,25 +2905,25 @@
         <v>Fuchs</v>
       </c>
       <c r="B133">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C133">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D133">
+        <v>6</v>
+      </c>
+      <c r="E133">
+        <v>6</v>
+      </c>
+      <c r="F133">
         <v>5</v>
       </c>
-      <c r="E133">
+      <c r="G133">
         <v>5</v>
       </c>
-      <c r="F133">
-        <v>4</v>
-      </c>
-      <c r="G133">
-        <v>4</v>
-      </c>
       <c r="H133">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I133">
         <v>3</v>
@@ -2888,10 +2947,10 @@
         <v>1</v>
       </c>
       <c r="P133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q133">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -2899,25 +2958,25 @@
         <v>Goonse</v>
       </c>
       <c r="B134">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C134">
+        <v>17</v>
+      </c>
+      <c r="D134">
+        <v>17</v>
+      </c>
+      <c r="E134">
+        <v>14</v>
+      </c>
+      <c r="F134">
         <v>16</v>
       </c>
-      <c r="D134">
-        <v>16</v>
-      </c>
-      <c r="E134">
-        <v>13</v>
-      </c>
-      <c r="F134">
-        <v>15</v>
-      </c>
       <c r="G134">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H134">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I134">
         <v>4</v>
@@ -2952,49 +3011,49 @@
         <v>Chäli</v>
       </c>
       <c r="B135">
+        <v>24</v>
+      </c>
+      <c r="C135">
+        <v>26</v>
+      </c>
+      <c r="D135">
+        <v>25</v>
+      </c>
+      <c r="E135">
+        <v>15</v>
+      </c>
+      <c r="F135">
+        <v>13</v>
+      </c>
+      <c r="G135">
+        <v>19</v>
+      </c>
+      <c r="H135">
+        <v>15</v>
+      </c>
+      <c r="I135">
+        <v>14</v>
+      </c>
+      <c r="J135">
+        <v>26</v>
+      </c>
+      <c r="K135">
+        <v>19</v>
+      </c>
+      <c r="L135">
         <v>23</v>
       </c>
-      <c r="C135">
-        <v>25</v>
-      </c>
-      <c r="D135">
+      <c r="M135">
         <v>24</v>
       </c>
-      <c r="E135">
+      <c r="N135">
+        <v>15</v>
+      </c>
+      <c r="O135">
+        <v>13</v>
+      </c>
+      <c r="P135">
         <v>14</v>
-      </c>
-      <c r="F135">
-        <v>12</v>
-      </c>
-      <c r="G135">
-        <v>18</v>
-      </c>
-      <c r="H135">
-        <v>14</v>
-      </c>
-      <c r="I135">
-        <v>13</v>
-      </c>
-      <c r="J135">
-        <v>25</v>
-      </c>
-      <c r="K135">
-        <v>18</v>
-      </c>
-      <c r="L135">
-        <v>22</v>
-      </c>
-      <c r="M135">
-        <v>23</v>
-      </c>
-      <c r="N135">
-        <v>14</v>
-      </c>
-      <c r="O135">
-        <v>12</v>
-      </c>
-      <c r="P135">
-        <v>13</v>
       </c>
       <c r="Q135">
         <v>12</v>
